--- a/转换稿/《北京工业志·电子志》2001 第四篇.xlsx
+++ b/转换稿/《北京工业志·电子志》2001 第四篇.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="待核·厂所" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="待核·补格子" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待核·补全已有记录" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="待核·器件" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="待核·整机" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="待核·名称沿革" sheetId="5" state="visible" r:id="rId5"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>↑ 一行 = 总表里某家的某一个格子。这些单位早已在总表里,「待核·厂所」那张不必再核一遍 —— 重跑一本核过的志书,所得就是这几格。「补」= 总表那一格空着,写 y 就填上去。「更细」= 总表里已有,而这一遍说得更具体(1987年 → 1987年5月):说的是一回事,不是两说。「对不上」= 两边都有值而不同:总表那一份是你核过的,写 y 才拿这一遍的盖过去,拿不准就空着。并表时只动写了 y 的那几格,别的一格不碰。</t>
+          <t>↑ **一行 = 总表里某一家的某一栏**,不是一家一行。这些单位早已在总表里(「待核·厂所」那张给它们标着「已收」),那张不必再核一遍 —— 重跑一本核过的志书,所得就是这几格。「补」= 总表那一格空着,写 y 就填上去。「更细」= 总表里已有,而这一遍说得更具体(1987年 → 1987年5月):说的是一回事,不是两说。「对不上」= 两边都有值而不同:总表那一份是你核过的,写 y 才拿这一遍的盖过去,拿不准就空着。并表时只动写了 y 的那几格,别的一格不碰。</t>
         </is>
       </c>
     </row>

--- a/转换稿/《北京工业志·电子志》2001 第四篇.xlsx
+++ b/转换稿/《北京工业志·电子志》2001 第四篇.xlsx
@@ -9650,7 +9650,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>总表现值</t>
+          <t>总表里原有的</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">

--- a/转换稿/《北京工业志·电子志》2001 第四篇.xlsx
+++ b/转换稿/《北京工业志·电子志》2001 第四篇.xlsx
@@ -9675,7 +9675,7 @@
       </c>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>↑ **一行 = 总表里某一家的某一栏**,不是一家一行。这些单位早已在总表里(「待核·厂所」那张给它们标着「已收」),那张不必再核一遍 —— 重跑一本核过的志书,所得就是这几格。「补」= 总表那一格空着,写 y 就填上去。「更细」= 总表里已有,而这一遍说得更具体(1987年 → 1987年5月):说的是一回事,不是两说。「对不上」= 两边都有值而不同:总表那一份是你核过的,写 y 才拿这一遍的盖过去,拿不准就空着。并表时只动写了 y 的那几格,别的一格不碰。</t>
+          <t>↑ **一行 = 总表里某一家的某一栏**,不是一家一行。这些单位早已在总表里(「待核·厂所」那张给它们标着「已收」),那张不必再核一遍 —— 重跑一本核过的志书,所得就是这几格。「补」= 总表那一格空着,写 y 就填上去。「更细」= 总表里已有,而这一遍说得更具体(1987年 → 1987年5月):说的是一回事,不是两说。「对不上」= 两边都有值而不同:总表那一份是你核过的,写 y 才拿这一遍的盖过去,拿不准就空着。**认错了就改「这一遍认出的」那一格** —— 进总表的就是它;「总表里原有的」「种类」「凭据」只供判断,改它不算数。并表时只动写了 y 的那几格,别的一格不碰。</t>
         </is>
       </c>
     </row>
